--- a/data/distribution_rewards/2026-09/finalized.xlsx
+++ b/data/distribution_rewards/2026-09/finalized.xlsx
@@ -630,7 +630,6 @@
           <t>USDS-CLE, USDS-GROVE, USDS-SKY, USDS-SPK, sUSDS, stUSDS</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,7 +766,6 @@
           <t>USDS-CLE, USDS-SKY, USDS-SPK, sUSDC, sUSDS, spETH, spPYUSD, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -810,7 +808,6 @@
           <t>sUSDC, sUSDS</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -912,23 +909,18 @@
           <t>132</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
         <v>0.01</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>0.27</v>
       </c>
       <c r="H11" t="n">
         <v>10.54</v>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
         <v>10.83</v>
       </c>
@@ -949,15 +941,6 @@
           <t>171</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
         <v>0.02</v>
       </c>
@@ -966,7 +949,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1009,7 +991,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1052,7 +1033,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1095,7 +1075,6 @@
           <t>sUSDC, sUSDS, spETH, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1138,7 +1117,6 @@
           <t>sUSDC, sUSDS, spUSDT</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1181,7 +1159,6 @@
           <t>sUSDC, sUSDS, spETH, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1224,7 +1201,6 @@
           <t>sUSDC, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1267,7 +1243,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1310,7 +1285,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1353,7 +1327,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1396,7 +1369,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1469,9 +1441,6 @@
       <c r="G24" t="n">
         <v>0.01</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
         <v>0.11</v>
       </c>
@@ -1480,7 +1449,6 @@
           <t>spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1523,7 +1491,6 @@
           <t>sUSDC, sUSDS, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1566,7 +1533,6 @@
           <t>spETH, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1574,7 +1540,6 @@
           <t>204</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>4.01</v>
       </c>
@@ -1607,7 +1572,6 @@
           <t>sUSDC, sUSDS, spETH, spUSDC</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1615,7 +1579,6 @@
           <t>205</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0.03</v>
       </c>
@@ -1648,7 +1611,6 @@
           <t>sUSDC, sUSDS, spETH, spUSDC</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1656,11 +1618,6 @@
           <t>214</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>0.15</v>
       </c>
@@ -1681,7 +1638,6 @@
           <t>spETH, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1689,8 +1645,6 @@
           <t>216</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>216.61</v>
       </c>
@@ -1720,7 +1674,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1728,12 +1681,6 @@
           <t>217</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>0.5</v>
       </c>
@@ -1751,7 +1698,6 @@
           <t>spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1759,17 +1705,9 @@
           <t>219</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>14.26</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="n">
         <v>14.26</v>
       </c>
@@ -1778,7 +1716,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1786,15 +1723,6 @@
           <t>223</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="n">
         <v>0.01</v>
       </c>
@@ -1803,7 +1731,6 @@
           <t>spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1811,10 +1738,6 @@
           <t>224</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
         <v>4582.17</v>
       </c>
@@ -1838,7 +1761,6 @@
           <t>USDS-SPK, sUSDS</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1846,14 +1768,6 @@
           <t>232</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>1262.03</v>
       </c>
@@ -1865,7 +1779,6 @@
           <t>sUSDS, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1873,14 +1786,6 @@
           <t>234</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>0.55</v>
       </c>
@@ -1892,7 +1797,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1900,15 +1804,6 @@
           <t>303</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="n">
         <v>0.01</v>
       </c>
@@ -1917,7 +1812,6 @@
           <t>USDS-SKY, sUSDS</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1925,15 +1819,6 @@
           <t>555</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="n">
         <v>0.03</v>
       </c>
@@ -1942,7 +1827,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1985,7 +1869,6 @@
           <t>USDS-CLE, USDS-SKY, sUSDS</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2028,7 +1911,6 @@
           <t>USDS-CLE, USDS-GROVE, USDS-SKY, USDS-SPK, sUSDS</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2165,7 +2047,6 @@
           <t>USDS-SKY, USDS-SPK, sUSDS</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2185,11 +2066,6 @@
       <c r="E44" t="n">
         <v>0.59</v>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="n">
         <v>1378.16</v>
       </c>
@@ -2245,7 +2121,6 @@
           <t>sUSDC, sUSDS, spETH, spUSDC, spUSDT</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2253,14 +2128,6 @@
           <t>1020</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>65.39</v>
       </c>
@@ -2272,7 +2139,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2281,34 +2147,34 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="C47" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="D47" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="E47" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="G47" t="n">
-        <v>6953.52</v>
+        <v>17103.06</v>
       </c>
       <c r="H47" t="n">
-        <v>8291.32</v>
+        <v>11730.41</v>
       </c>
       <c r="I47" t="n">
-        <v>12492.55</v>
+        <v>12719.45</v>
       </c>
       <c r="J47" t="n">
-        <v>15124.25</v>
+        <v>14902.21</v>
       </c>
       <c r="K47" t="n">
-        <v>42864.48</v>
+        <v>56462.25</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2317,7 +2183,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -2327,31 +2193,29 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="E48" t="n">
-        <v>6454.4</v>
+        <v>15875.41</v>
       </c>
       <c r="F48" t="n">
-        <v>7020.72</v>
+        <v>17843.96</v>
       </c>
       <c r="G48" t="n">
-        <v>4810.91</v>
+        <v>11833.05</v>
       </c>
       <c r="H48" t="n">
-        <v>4923.13</v>
+        <v>6767.26</v>
       </c>
       <c r="I48" t="n">
-        <v>5594.93</v>
+        <v>5696.55</v>
       </c>
       <c r="J48" t="n">
-        <v>5262.77</v>
+        <v>5185.51</v>
       </c>
       <c r="K48" t="n">
-        <v>39491.94</v>
+        <v>76990.19</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2360,7 +2224,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -2371,34 +2235,34 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="C49" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="D49" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="E49" t="n">
-        <v>26.6</v>
+        <v>65.42</v>
       </c>
       <c r="F49" t="n">
-        <v>30.34</v>
+        <v>77.12</v>
       </c>
       <c r="G49" t="n">
-        <v>20.24</v>
+        <v>49.77</v>
       </c>
       <c r="H49" t="n">
-        <v>21.14</v>
+        <v>29.93</v>
       </c>
       <c r="I49" t="n">
-        <v>27.72</v>
+        <v>28.22</v>
       </c>
       <c r="J49" t="n">
-        <v>20.65</v>
+        <v>20.35</v>
       </c>
       <c r="K49" t="n">
-        <v>779.4</v>
+        <v>1803.23</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2407,7 +2271,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -2417,9 +2281,6 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
         <v>82.23999999999999</v>
       </c>
@@ -2446,7 +2307,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2454,19 +2314,12 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>174574.28</v>
       </c>
       <c r="E51" t="n">
         <v>116737.37</v>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>291311.65</v>
       </c>
@@ -2475,7 +2328,6 @@
           <t>sUSDS, stUSDS</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2483,18 +2335,12 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>17144.97</v>
       </c>
       <c r="E52" t="n">
         <v>8259.879999999999</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>3004.45</v>
       </c>
@@ -2506,7 +2352,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2514,10 +2359,6 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
         <v>12035.78</v>
       </c>
@@ -2541,7 +2382,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2549,14 +2389,6 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>549.8099999999999</v>
       </c>
@@ -2568,7 +2400,6 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2576,12 +2407,6 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>2834.56</v>
       </c>
@@ -2599,7 +2424,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2607,19 +2431,12 @@
           <t>2222</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
         <v>10.68</v>
       </c>
       <c r="F56" t="n">
         <v>14.75</v>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
         <v>25.42</v>
       </c>
@@ -2628,7 +2445,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2636,11 +2452,6 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>5.66</v>
       </c>
@@ -2661,7 +2472,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2669,15 +2479,6 @@
           <t>3001</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
         <v>0.01</v>
       </c>
@@ -2686,7 +2487,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2694,12 +2494,6 @@
           <t>3006</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>0.77</v>
       </c>
@@ -2717,7 +2511,6 @@
           <t>sUSDC, sUSDS</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2725,14 +2518,6 @@
           <t>3007</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>0.36</v>
       </c>
@@ -2744,7 +2529,6 @@
           <t>sUSDS, stUSDS</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2752,14 +2536,6 @@
           <t>3008</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>30.6</v>
       </c>
@@ -2771,7 +2547,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2779,13 +2554,6 @@
           <t>3009</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>21.19</v>
       </c>
@@ -2800,7 +2568,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2843,7 +2610,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2898,14 +2664,9 @@
           <t>4011</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>76.34</v>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>119.5</v>
       </c>
@@ -2982,15 +2743,6 @@
           <t>9998</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>0.01</v>
       </c>
@@ -2999,7 +2751,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3136,7 +2887,6 @@
           <t>USDS-SKY, sUSDS</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3270,7 +3020,6 @@
       <c r="F4" t="n">
         <v>339149.15</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3295,7 +3044,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3349,7 +3097,6 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3374,7 +3121,6 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3428,7 +3174,6 @@
       <c r="F10" t="n">
         <v>-411524.84</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3453,7 +3198,6 @@
       <c r="F11" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3565,7 +3309,6 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3590,7 +3333,6 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3615,7 +3357,6 @@
       <c r="F17" t="n">
         <v>0.06</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3640,7 +3381,6 @@
       <c r="F18" t="n">
         <v>1.27</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3665,7 +3405,6 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3690,7 +3429,6 @@
       <c r="F20" t="n">
         <v>-800.41</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3715,7 +3453,6 @@
       <c r="F21" t="n">
         <v>-7343.16</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3740,7 +3477,6 @@
       <c r="F22" t="n">
         <v>-27969.67</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3765,7 +3501,6 @@
       <c r="F23" t="n">
         <v>-21707.31</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3790,7 +3525,6 @@
       <c r="F24" t="n">
         <v>17.57</v>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3810,12 +3544,11 @@
         <v>-0.05</v>
       </c>
       <c r="E25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3840,7 +3573,6 @@
       <c r="F26" t="n">
         <v>1.7</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3863,9 +3595,8 @@
         <v>-0.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3919,7 +3650,6 @@
       <c r="F29" t="n">
         <v>0.06</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3944,7 +3674,6 @@
       <c r="F30" t="n">
         <v>-10.89</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3969,7 +3698,6 @@
       <c r="F31" t="n">
         <v>-135.74</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3994,7 +3722,6 @@
       <c r="F32" t="n">
         <v>-3.99</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4019,7 +3746,6 @@
       <c r="F33" t="n">
         <v>-0.27</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4044,7 +3770,6 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4069,7 +3794,6 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4094,7 +3818,6 @@
       <c r="F36" t="n">
         <v>0.11</v>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4119,7 +3842,6 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4144,7 +3866,6 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4169,7 +3890,6 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4194,7 +3914,6 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4219,7 +3938,6 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4244,7 +3962,6 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4269,7 +3986,6 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4294,7 +4010,6 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4319,7 +4034,6 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4344,7 +4058,6 @@
       <c r="F46" t="n">
         <v>3244.48</v>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4369,7 +4082,6 @@
       <c r="F47" t="n">
         <v>14.25</v>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4452,7 +4164,6 @@
       <c r="F50" t="n">
         <v>5.5</v>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4477,7 +4188,6 @@
       <c r="F51" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4531,7 +4241,6 @@
       <c r="F53" t="n">
         <v>-0.18</v>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4556,7 +4265,6 @@
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4570,20 +4278,20 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="D55" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E55" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="F55" t="n">
-        <v>0.99</v>
+        <v>2.45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -4605,14 +4313,14 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="F56" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -4628,20 +4336,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="D57" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="E57" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="F57" t="n">
-        <v>632.72</v>
+        <v>1532.43</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4376,6 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4693,7 +4400,6 @@
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4718,7 +4424,6 @@
       <c r="F60" t="n">
         <v>61.28</v>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4743,7 +4448,6 @@
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4768,7 +4472,6 @@
       <c r="F62" t="n">
         <v>15.07</v>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4793,7 +4496,6 @@
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4818,7 +4520,6 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4843,7 +4544,6 @@
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4868,7 +4568,6 @@
       <c r="F66" t="n">
         <v>0</v>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4893,7 +4592,6 @@
       <c r="F67" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4918,7 +4616,6 @@
       <c r="F68" t="n">
         <v>0</v>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4943,7 +4640,6 @@
       <c r="F69" t="n">
         <v>0</v>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4968,7 +4664,6 @@
       <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4993,7 +4688,6 @@
       <c r="F71" t="n">
         <v>0</v>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5018,7 +4712,6 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5043,7 +4736,6 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5068,7 +4760,6 @@
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5093,7 +4784,6 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5118,7 +4808,6 @@
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5143,7 +4832,6 @@
       <c r="F77" t="n">
         <v>1.6</v>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5168,7 +4856,6 @@
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5251,7 +4938,6 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5305,7 +4991,6 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5388,7 +5073,6 @@
       <c r="F86" t="n">
         <v>2490.99</v>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5550,7 +5234,6 @@
       <c r="H4" t="n">
         <v>-3273.59</v>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5581,7 +5264,6 @@
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5647,7 +5329,6 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5678,7 +5359,6 @@
       <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5744,7 +5424,6 @@
       <c r="H10" t="n">
         <v>781505.25</v>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5758,13 +5437,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>-0.01</v>
@@ -5775,7 +5454,6 @@
       <c r="H11" t="n">
         <v>0.35</v>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5911,7 +5589,6 @@
       <c r="H15" t="n">
         <v>0</v>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5942,7 +5619,6 @@
       <c r="H16" t="n">
         <v>0</v>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5973,7 +5649,6 @@
       <c r="H17" t="n">
         <v>0.01</v>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6004,7 +5679,6 @@
       <c r="H18" t="n">
         <v>-80.34</v>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6035,7 +5709,6 @@
       <c r="H19" t="n">
         <v>0</v>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6066,7 +5739,6 @@
       <c r="H20" t="n">
         <v>2813.75</v>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6097,7 +5769,6 @@
       <c r="H21" t="n">
         <v>26432.77</v>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6128,7 +5799,6 @@
       <c r="H22" t="n">
         <v>25526.72</v>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6159,7 +5829,6 @@
       <c r="H23" t="n">
         <v>52664.59</v>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6190,7 +5859,6 @@
       <c r="H24" t="n">
         <v>15605.57</v>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6210,10 +5878,10 @@
         <v>-0.01</v>
       </c>
       <c r="E25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>2.63</v>
@@ -6221,7 +5889,6 @@
       <c r="H25" t="n">
         <v>2.61</v>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6252,7 +5919,6 @@
       <c r="H26" t="n">
         <v>1826.32</v>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6275,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0.15</v>
@@ -6283,7 +5949,6 @@
       <c r="H27" t="n">
         <v>0.15</v>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6349,7 +6014,6 @@
       <c r="H29" t="n">
         <v>0.1</v>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6380,7 +6044,6 @@
       <c r="H30" t="n">
         <v>132.64</v>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6411,7 +6074,6 @@
       <c r="H31" t="n">
         <v>181.9</v>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6442,7 +6104,6 @@
       <c r="H32" t="n">
         <v>53.03</v>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6473,7 +6134,6 @@
       <c r="H33" t="n">
         <v>0.63</v>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6504,7 +6164,6 @@
       <c r="H34" t="n">
         <v>0</v>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6535,7 +6194,6 @@
       <c r="H35" t="n">
         <v>0</v>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6566,7 +6224,6 @@
       <c r="H36" t="n">
         <v>282.14</v>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6597,7 +6254,6 @@
       <c r="H37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6628,7 +6284,6 @@
       <c r="H38" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6659,7 +6314,6 @@
       <c r="H39" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6690,7 +6344,6 @@
       <c r="H40" t="n">
         <v>-5.46</v>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6721,7 +6374,6 @@
       <c r="H41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6752,7 +6404,6 @@
       <c r="H42" t="n">
         <v>0</v>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6783,7 +6434,6 @@
       <c r="H43" t="n">
         <v>0</v>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6814,7 +6464,6 @@
       <c r="H44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6845,7 +6494,6 @@
       <c r="H45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6876,7 +6524,6 @@
       <c r="H46" t="n">
         <v>223.61</v>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6907,7 +6554,6 @@
       <c r="H47" t="n">
         <v>-120.13</v>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7008,7 +6654,6 @@
       <c r="H50" t="n">
         <v>-76.86</v>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7039,7 +6684,6 @@
       <c r="H51" t="n">
         <v>0</v>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7062,7 +6706,7 @@
         <v>-0.01</v>
       </c>
       <c r="F52" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -7105,7 +6749,6 @@
       <c r="H53" t="n">
         <v>3.73</v>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7136,7 +6779,6 @@
       <c r="H54" t="n">
         <v>0</v>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7150,26 +6792,26 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="D55" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E55" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="F55" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="G55" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="H55" t="n">
-        <v>2.83</v>
+        <v>7.12</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -7191,20 +6833,20 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="F56" t="n">
-        <v>6454.4</v>
+        <v>15875.41</v>
       </c>
       <c r="G56" t="n">
-        <v>7020.72</v>
+        <v>17843.96</v>
       </c>
       <c r="H56" t="n">
-        <v>18900.2</v>
+        <v>47507.82</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -7220,26 +6862,26 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="D57" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="E57" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="F57" t="n">
-        <v>26.6</v>
+        <v>65.42</v>
       </c>
       <c r="G57" t="n">
-        <v>30.34</v>
+        <v>77.12</v>
       </c>
       <c r="H57" t="n">
-        <v>689.66</v>
+        <v>1674.97</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -7272,7 +6914,6 @@
       <c r="H58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7303,7 +6944,6 @@
       <c r="H59" t="n">
         <v>-10.19</v>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7334,7 +6974,6 @@
       <c r="H60" t="n">
         <v>-346.82</v>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7365,7 +7004,6 @@
       <c r="H61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7396,7 +7034,6 @@
       <c r="H62" t="n">
         <v>-30.24</v>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7427,7 +7064,6 @@
       <c r="H63" t="n">
         <v>-14.33</v>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7458,7 +7094,6 @@
       <c r="H64" t="n">
         <v>0</v>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7489,7 +7124,6 @@
       <c r="H65" t="n">
         <v>0</v>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7520,7 +7154,6 @@
       <c r="H66" t="n">
         <v>0</v>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7551,7 +7184,6 @@
       <c r="H67" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7582,7 +7214,6 @@
       <c r="H68" t="n">
         <v>0</v>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7613,7 +7244,6 @@
       <c r="H69" t="n">
         <v>0</v>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7644,7 +7274,6 @@
       <c r="H70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7675,7 +7304,6 @@
       <c r="H71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7706,7 +7334,6 @@
       <c r="H72" t="n">
         <v>0</v>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7737,7 +7364,6 @@
       <c r="H73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7768,7 +7394,6 @@
       <c r="H74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7799,7 +7424,6 @@
       <c r="H75" t="n">
         <v>0</v>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7830,7 +7454,6 @@
       <c r="H76" t="n">
         <v>0</v>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7853,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>-0.01</v>
@@ -7861,7 +7484,6 @@
       <c r="H77" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7892,7 +7514,6 @@
       <c r="H78" t="n">
         <v>0</v>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7993,7 +7614,6 @@
       <c r="H81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8059,7 +7679,6 @@
       <c r="H83" t="n">
         <v>0</v>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8160,7 +7779,6 @@
       <c r="H86" t="n">
         <v>-3.75</v>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8191,7 +7809,6 @@
       <c r="H87" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8222,7 +7839,6 @@
       <c r="H88" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8356,7 +7972,6 @@
       <c r="F4" t="n">
         <v>-28520.15</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8381,7 +7996,6 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8435,7 +8049,6 @@
       <c r="F7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8460,7 +8073,6 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8514,7 +8126,6 @@
       <c r="F10" t="n">
         <v>-413013.14</v>
       </c>
-      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8539,7 +8150,6 @@
       <c r="F11" t="n">
         <v>-0.03</v>
       </c>
-      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8651,7 +8261,6 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8676,7 +8285,6 @@
       <c r="F16" t="n">
         <v>0</v>
       </c>
-      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8701,7 +8309,6 @@
       <c r="F17" t="n">
         <v>0.06</v>
       </c>
-      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8726,7 +8333,6 @@
       <c r="F18" t="n">
         <v>1.27</v>
       </c>
-      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8751,7 +8357,6 @@
       <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8776,7 +8381,6 @@
       <c r="F20" t="n">
         <v>-800.41</v>
       </c>
-      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8801,7 +8405,6 @@
       <c r="F21" t="n">
         <v>-7346.16</v>
       </c>
-      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8826,7 +8429,6 @@
       <c r="F22" t="n">
         <v>-27969.67</v>
       </c>
-      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -8851,7 +8453,6 @@
       <c r="F23" t="n">
         <v>-21707.31</v>
       </c>
-      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8876,7 +8477,6 @@
       <c r="F24" t="n">
         <v>17.57</v>
       </c>
-      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -8896,12 +8496,11 @@
         <v>-0.05</v>
       </c>
       <c r="E25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>-0.09</v>
       </c>
-      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8926,7 +8525,6 @@
       <c r="F26" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8949,9 +8547,8 @@
         <v>-0.05</v>
       </c>
       <c r="F27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9005,7 +8602,6 @@
       <c r="F29" t="n">
         <v>0.06</v>
       </c>
-      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9030,7 +8626,6 @@
       <c r="F30" t="n">
         <v>-10.89</v>
       </c>
-      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9055,7 +8650,6 @@
       <c r="F31" t="n">
         <v>-135.74</v>
       </c>
-      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9080,7 +8674,6 @@
       <c r="F32" t="n">
         <v>-3.99</v>
       </c>
-      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -9105,7 +8698,6 @@
       <c r="F33" t="n">
         <v>-0.27</v>
       </c>
-      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9130,7 +8722,6 @@
       <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9155,7 +8746,6 @@
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9180,7 +8770,6 @@
       <c r="F36" t="n">
         <v>0.11</v>
       </c>
-      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9205,7 +8794,6 @@
       <c r="F37" t="n">
         <v>0</v>
       </c>
-      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -9230,7 +8818,6 @@
       <c r="F38" t="n">
         <v>0</v>
       </c>
-      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -9255,7 +8842,6 @@
       <c r="F39" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -9280,7 +8866,6 @@
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -9305,7 +8890,6 @@
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -9330,7 +8914,6 @@
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -9355,7 +8938,6 @@
       <c r="F43" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -9380,7 +8962,6 @@
       <c r="F44" t="n">
         <v>0</v>
       </c>
-      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -9405,7 +8986,6 @@
       <c r="F45" t="n">
         <v>0</v>
       </c>
-      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -9430,7 +9010,6 @@
       <c r="F46" t="n">
         <v>3244.48</v>
       </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9455,7 +9034,6 @@
       <c r="F47" t="n">
         <v>14.25</v>
       </c>
-      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9538,7 +9116,6 @@
       <c r="F50" t="n">
         <v>25.9</v>
       </c>
-      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9563,7 +9140,6 @@
       <c r="F51" t="n">
         <v>0</v>
       </c>
-      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9617,7 +9193,6 @@
       <c r="F53" t="n">
         <v>-0.18</v>
       </c>
-      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9642,7 +9217,6 @@
       <c r="F54" t="n">
         <v>0</v>
       </c>
-      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9656,20 +9230,20 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="D55" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E55" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="F55" t="n">
-        <v>0.99</v>
+        <v>2.45</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -9691,14 +9265,14 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="F56" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -9714,20 +9288,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="D57" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="E57" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="F57" t="n">
-        <v>632.72</v>
+        <v>1532.43</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9328,6 @@
       <c r="F58" t="n">
         <v>0</v>
       </c>
-      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9779,7 +9352,6 @@
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9804,7 +9376,6 @@
       <c r="F60" t="n">
         <v>61.28</v>
       </c>
-      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9829,7 +9400,6 @@
       <c r="F61" t="n">
         <v>0</v>
       </c>
-      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9854,7 +9424,6 @@
       <c r="F62" t="n">
         <v>15.07</v>
       </c>
-      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9879,7 +9448,6 @@
       <c r="F63" t="n">
         <v>0</v>
       </c>
-      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9904,7 +9472,6 @@
       <c r="F64" t="n">
         <v>0</v>
       </c>
-      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9929,7 +9496,6 @@
       <c r="F65" t="n">
         <v>0</v>
       </c>
-      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9954,7 +9520,6 @@
       <c r="F66" t="n">
         <v>0</v>
       </c>
-      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -9979,7 +9544,6 @@
       <c r="F67" t="n">
         <v>0</v>
       </c>
-      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10004,7 +9568,6 @@
       <c r="F68" t="n">
         <v>0</v>
       </c>
-      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10029,7 +9592,6 @@
       <c r="F69" t="n">
         <v>0</v>
       </c>
-      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10054,7 +9616,6 @@
       <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10079,7 +9640,6 @@
       <c r="F71" t="n">
         <v>0</v>
       </c>
-      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10104,7 +9664,6 @@
       <c r="F72" t="n">
         <v>0</v>
       </c>
-      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10129,7 +9688,6 @@
       <c r="F73" t="n">
         <v>0</v>
       </c>
-      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10154,7 +9712,6 @@
       <c r="F74" t="n">
         <v>0</v>
       </c>
-      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -10179,7 +9736,6 @@
       <c r="F75" t="n">
         <v>0</v>
       </c>
-      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10204,7 +9760,6 @@
       <c r="F76" t="n">
         <v>0</v>
       </c>
-      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10229,7 +9784,6 @@
       <c r="F77" t="n">
         <v>1.6</v>
       </c>
-      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10254,7 +9808,6 @@
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10337,7 +9890,6 @@
       <c r="F81" t="n">
         <v>0</v>
       </c>
-      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10391,7 +9943,6 @@
       <c r="F83" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10474,7 +10025,6 @@
       <c r="F86" t="n">
         <v>2490.99</v>
       </c>
-      <c r="G86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10782,12 +10332,6 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>540.21</v>
       </c>
@@ -10911,15 +10455,6 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>0</v>
       </c>
@@ -10987,8 +10522,6 @@
           <t>USDS-CLE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>324.57</v>
       </c>
@@ -11030,17 +10563,9 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>22.62</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>22.62</v>
       </c>
@@ -11108,8 +10633,6 @@
           <t>USDS-SPK</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>180.6</v>
       </c>
@@ -11245,13 +10768,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>2.66</v>
       </c>
@@ -11278,15 +10794,6 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>0</v>
       </c>
@@ -11307,19 +10814,12 @@
           <t>stUSDS</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>0.01</v>
       </c>
       <c r="J16" t="n">
         <v>0.01</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>0.04</v>
       </c>
@@ -11370,7 +10870,6 @@
       <c r="L17" t="n">
         <v>44107.29</v>
       </c>
-      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11383,12 +10882,6 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>31984.31</v>
       </c>
@@ -11401,7 +10894,6 @@
       <c r="L18" t="n">
         <v>89004.64999999999</v>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11444,7 +10936,6 @@
       <c r="L19" t="n">
         <v>39634.15</v>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11487,7 +10978,6 @@
       <c r="L20" t="n">
         <v>80035.17999999999</v>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11530,7 +11020,6 @@
       <c r="L21" t="n">
         <v>635276.71</v>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11573,7 +11062,6 @@
       <c r="L22" t="n">
         <v>26020.6</v>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11586,19 +11074,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11658,19 +11136,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11683,19 +11151,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11785,7 +11243,6 @@
       <c r="L28" t="n">
         <v>24297.97</v>
       </c>
-      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11828,7 +11285,6 @@
       <c r="L29" t="n">
         <v>32992.76</v>
       </c>
-      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11871,7 +11327,6 @@
       <c r="L30" t="n">
         <v>1928815.9</v>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11914,7 +11369,6 @@
       <c r="L31" t="n">
         <v>1003559.73</v>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11957,7 +11411,6 @@
       <c r="L32" t="n">
         <v>5421871.24</v>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11970,19 +11423,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12025,7 +11468,6 @@
       <c r="L34" t="n">
         <v>663.25</v>
       </c>
-      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12068,7 +11510,6 @@
       <c r="L35" t="n">
         <v>522416.93</v>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12111,7 +11552,6 @@
       <c r="L36" t="n">
         <v>664228.24</v>
       </c>
-      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12154,7 +11594,6 @@
       <c r="L37" t="n">
         <v>150.45</v>
       </c>
-      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12167,7 +11606,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>0.29</v>
       </c>
@@ -12195,7 +11633,6 @@
       <c r="L38" t="n">
         <v>4</v>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12302,23 +11739,18 @@
           <t>spPYUSD</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>0.01</v>
       </c>
       <c r="F41" t="n">
         <v>0.01</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>0.27</v>
       </c>
       <c r="I41" t="n">
         <v>10.54</v>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>10.83</v>
       </c>
@@ -12339,19 +11771,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12364,19 +11786,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>0.02</v>
       </c>
-      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12419,7 +11831,6 @@
       <c r="L44" t="n">
         <v>0.18</v>
       </c>
-      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12462,7 +11873,6 @@
       <c r="L45" t="n">
         <v>89091.17</v>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12475,19 +11885,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>0</v>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12500,19 +11900,9 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>0</v>
       </c>
-      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12525,19 +11915,9 @@
           <t>stUSDS</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
         <v>0</v>
       </c>
-      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12580,7 +11960,6 @@
       <c r="L49" t="n">
         <v>7082.07</v>
       </c>
-      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12599,17 +11978,9 @@
       <c r="D50" t="n">
         <v>0.02</v>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>0.06</v>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12622,19 +11993,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12677,7 +12038,6 @@
       <c r="L52" t="n">
         <v>7270.07</v>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12720,7 +12080,6 @@
       <c r="L53" t="n">
         <v>1953.14</v>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12763,7 +12122,6 @@
       <c r="L54" t="n">
         <v>13309.42</v>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12776,10 +12134,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>3610.21</v>
       </c>
@@ -12798,7 +12152,6 @@
       <c r="L55" t="n">
         <v>65296.1</v>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12811,8 +12164,6 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
         <v>5889.44</v>
       </c>
@@ -12837,7 +12188,6 @@
       <c r="L56" t="n">
         <v>53023.42</v>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12871,12 +12221,9 @@
       <c r="I57" t="n">
         <v>0.01</v>
       </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>197.72</v>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12892,8 +12239,6 @@
       <c r="C58" t="n">
         <v>0.16</v>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>7.62</v>
       </c>
@@ -12903,13 +12248,9 @@
       <c r="H58" t="n">
         <v>4.86</v>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>19.44</v>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12922,19 +12263,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12977,7 +12308,6 @@
       <c r="L60" t="n">
         <v>27278.15</v>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -13020,7 +12350,6 @@
       <c r="L61" t="n">
         <v>699.61</v>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13033,8 +12362,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
         <v>479.85</v>
       </c>
@@ -13059,7 +12386,6 @@
       <c r="L62" t="n">
         <v>13408.43</v>
       </c>
-      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13102,7 +12428,6 @@
       <c r="L63" t="n">
         <v>2389.96</v>
       </c>
-      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13145,7 +12470,6 @@
       <c r="L64" t="n">
         <v>132296.98</v>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -13188,7 +12512,6 @@
       <c r="L65" t="n">
         <v>291628.71</v>
       </c>
-      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13231,7 +12554,6 @@
       <c r="L66" t="n">
         <v>32.3</v>
       </c>
-      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13274,7 +12596,6 @@
       <c r="L67" t="n">
         <v>23349.73</v>
       </c>
-      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13317,7 +12638,6 @@
       <c r="L68" t="n">
         <v>1.6</v>
       </c>
-      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13395,13 +12715,9 @@
       <c r="H70" t="n">
         <v>0.01</v>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>0.09</v>
       </c>
-      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13414,19 +12730,9 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>0.01</v>
       </c>
-      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13439,23 +12745,15 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
         <v>0.13</v>
       </c>
       <c r="E72" t="n">
         <v>0.14</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>0.27</v>
       </c>
-      <c r="M72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13468,11 +12766,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>1650.1</v>
       </c>
@@ -13488,7 +12781,6 @@
       <c r="L73" t="n">
         <v>15866.23</v>
       </c>
-      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13501,7 +12793,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
         <v>0.59</v>
       </c>
@@ -13529,7 +12820,6 @@
       <c r="L74" t="n">
         <v>377.04</v>
       </c>
-      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -13545,7 +12835,6 @@
       <c r="C75" t="n">
         <v>2.1</v>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>0.48</v>
       </c>
@@ -13555,7 +12844,6 @@
       <c r="G75" t="n">
         <v>0.02</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>2.54</v>
       </c>
@@ -13568,7 +12856,6 @@
       <c r="L75" t="n">
         <v>150.51</v>
       </c>
-      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13581,19 +12868,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>0</v>
       </c>
-      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13636,7 +12913,6 @@
       <c r="L77" t="n">
         <v>54.18</v>
       </c>
-      <c r="M77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13679,7 +12955,6 @@
       <c r="L78" t="n">
         <v>262</v>
       </c>
-      <c r="M78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13692,7 +12967,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
         <v>4.01</v>
       </c>
@@ -13720,7 +12994,6 @@
       <c r="L79" t="n">
         <v>261.95</v>
       </c>
-      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13733,9 +13006,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
         <v>0.01</v>
       </c>
@@ -13745,15 +13015,12 @@
       <c r="H80" t="n">
         <v>0.01</v>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="n">
         <v>0.02</v>
       </c>
       <c r="L80" t="n">
         <v>0.06</v>
       </c>
-      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13766,19 +13033,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13791,23 +13048,15 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>3.08</v>
       </c>
       <c r="F82" t="n">
         <v>4.56</v>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
         <v>7.64</v>
       </c>
-      <c r="M82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13820,21 +13069,12 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
         <v>0.02</v>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>0.02</v>
       </c>
-      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13847,19 +13087,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
         <v>0</v>
       </c>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13872,19 +13102,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
         <v>0</v>
       </c>
-      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13897,7 +13117,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
         <v>0.01</v>
       </c>
@@ -13925,7 +13144,6 @@
       <c r="L86" t="n">
         <v>1.45</v>
       </c>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13938,19 +13156,9 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13963,19 +13171,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13988,11 +13186,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>0.15</v>
       </c>
@@ -14008,7 +13201,6 @@
       <c r="L89" t="n">
         <v>72.38</v>
       </c>
-      <c r="M89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14021,12 +13213,6 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>0.65</v>
       </c>
@@ -14039,7 +13225,6 @@
       <c r="L90" t="n">
         <v>6.98</v>
       </c>
-      <c r="M90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14052,8 +13237,6 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
         <v>216.61</v>
       </c>
@@ -14078,7 +13261,6 @@
       <c r="L91" t="n">
         <v>2103.49</v>
       </c>
-      <c r="M91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14091,12 +13273,6 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="n">
         <v>0.5</v>
       </c>
@@ -14109,7 +13285,6 @@
       <c r="L92" t="n">
         <v>112.39</v>
       </c>
-      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -14122,13 +13297,6 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>11.17</v>
       </c>
@@ -14138,7 +13306,6 @@
       <c r="L93" t="n">
         <v>220.51</v>
       </c>
-      <c r="M93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -14151,21 +13318,12 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
         <v>14.26</v>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
         <v>14.26</v>
       </c>
-      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -14178,19 +13336,9 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
         <v>0.01</v>
       </c>
-      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -14203,19 +13351,9 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -14228,10 +13366,6 @@
           <t>USDS-SPK</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>397</v>
       </c>
@@ -14250,7 +13384,6 @@
       <c r="L97" t="n">
         <v>4006.02</v>
       </c>
-      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -14263,10 +13396,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>4185.17</v>
       </c>
@@ -14285,7 +13414,6 @@
       <c r="L98" t="n">
         <v>24054.82</v>
       </c>
-      <c r="M98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14298,21 +13426,12 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="n">
         <v>1223.48</v>
       </c>
       <c r="L99" t="n">
         <v>1223.48</v>
       </c>
-      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14325,21 +13444,12 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="n">
         <v>3.16</v>
       </c>
       <c r="L100" t="n">
         <v>3.16</v>
       </c>
-      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14352,21 +13462,12 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>35.38</v>
       </c>
       <c r="L101" t="n">
         <v>35.38</v>
       </c>
-      <c r="M101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -14379,21 +13480,12 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
         <v>0.55</v>
       </c>
       <c r="L102" t="n">
         <v>0.55</v>
       </c>
-      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -14406,19 +13498,9 @@
           <t>USDS-SKY</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14431,19 +13513,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
         <v>0.01</v>
       </c>
-      <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14456,19 +13528,9 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
         <v>0.03</v>
       </c>
-      <c r="M105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14481,19 +13543,9 @@
           <t>spUSDT</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
         <v>0</v>
       </c>
-      <c r="M106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14536,7 +13588,6 @@
       <c r="L107" t="n">
         <v>335.03</v>
       </c>
-      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14579,7 +13630,6 @@
       <c r="L108" t="n">
         <v>3704.58</v>
       </c>
-      <c r="M108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14622,7 +13672,6 @@
       <c r="L109" t="n">
         <v>5602.31</v>
       </c>
-      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14665,7 +13714,6 @@
       <c r="L110" t="n">
         <v>75.45999999999999</v>
       </c>
-      <c r="M110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14678,12 +13726,6 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="n">
         <v>164.09</v>
       </c>
@@ -14696,7 +13738,6 @@
       <c r="L111" t="n">
         <v>385.69</v>
       </c>
-      <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14739,7 +13780,6 @@
       <c r="L112" t="n">
         <v>8.789999999999999</v>
       </c>
-      <c r="M112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14752,19 +13792,9 @@
           <t>USDS-SPK</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
         <v>0</v>
       </c>
-      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14807,7 +13837,6 @@
       <c r="L114" t="n">
         <v>181733.22</v>
       </c>
-      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14991,7 +14020,6 @@
       <c r="L118" t="n">
         <v>6819.03</v>
       </c>
-      <c r="M118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15019,14 +14047,9 @@
       <c r="G119" t="n">
         <v>1445.04</v>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>18697.88</v>
       </c>
-      <c r="M119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15054,14 +14077,9 @@
       <c r="G120" t="n">
         <v>9316.85</v>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
         <v>39045.72</v>
       </c>
-      <c r="M120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15074,19 +14092,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
         <v>0</v>
       </c>
-      <c r="M121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15111,11 +14119,6 @@
       <c r="F122" t="n">
         <v>0.15</v>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>1377.72</v>
       </c>
@@ -15136,17 +14139,9 @@
           <t>USDS-SPK</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
       <c r="F123" t="n">
         <v>0.44</v>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
         <v>0.44</v>
       </c>
@@ -15197,7 +14192,6 @@
       <c r="L124" t="n">
         <v>1496.19</v>
       </c>
-      <c r="M124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15240,7 +14234,6 @@
       <c r="L125" t="n">
         <v>1.19</v>
       </c>
-      <c r="M125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15253,19 +14246,9 @@
           <t>spETH</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
         <v>0</v>
       </c>
-      <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15308,7 +14291,6 @@
       <c r="L127" t="n">
         <v>0.46</v>
       </c>
-      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15324,18 +14306,9 @@
       <c r="C128" t="n">
         <v>0.04</v>
       </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
         <v>0.04</v>
       </c>
-      <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15348,21 +14321,12 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
       <c r="K129" t="n">
         <v>65.39</v>
       </c>
       <c r="L129" t="n">
         <v>65.39</v>
       </c>
-      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15376,38 +14340,38 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="D130" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E130" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="F130" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="G130" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="H130" t="n">
-        <v>6953.52</v>
+        <v>17103.06</v>
       </c>
       <c r="I130" t="n">
-        <v>8291.32</v>
+        <v>11730.41</v>
       </c>
       <c r="J130" t="n">
-        <v>12492.55</v>
+        <v>12719.45</v>
       </c>
       <c r="K130" t="n">
-        <v>15124.25</v>
+        <v>14902.21</v>
       </c>
       <c r="L130" t="n">
-        <v>42864.48</v>
+        <v>56462.25</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -15422,35 +14386,33 @@
           <t>USDS</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="F131" t="n">
-        <v>6454.4</v>
+        <v>15875.41</v>
       </c>
       <c r="G131" t="n">
-        <v>7020.72</v>
+        <v>17843.96</v>
       </c>
       <c r="H131" t="n">
-        <v>4810.91</v>
+        <v>11833.05</v>
       </c>
       <c r="I131" t="n">
-        <v>4923.13</v>
+        <v>6767.26</v>
       </c>
       <c r="J131" t="n">
-        <v>5594.93</v>
+        <v>5696.55</v>
       </c>
       <c r="K131" t="n">
-        <v>5262.77</v>
+        <v>5185.51</v>
       </c>
       <c r="L131" t="n">
-        <v>39491.94</v>
+        <v>76990.19</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -15466,38 +14428,38 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="D132" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="E132" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="F132" t="n">
-        <v>26.6</v>
+        <v>65.42</v>
       </c>
       <c r="G132" t="n">
-        <v>30.34</v>
+        <v>77.12</v>
       </c>
       <c r="H132" t="n">
-        <v>20.24</v>
+        <v>49.77</v>
       </c>
       <c r="I132" t="n">
-        <v>21.14</v>
+        <v>29.93</v>
       </c>
       <c r="J132" t="n">
-        <v>27.72</v>
+        <v>28.22</v>
       </c>
       <c r="K132" t="n">
-        <v>20.65</v>
+        <v>20.35</v>
       </c>
       <c r="L132" t="n">
-        <v>779.4</v>
+        <v>1803.23</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -15512,19 +14474,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
       <c r="L133" t="n">
         <v>0</v>
       </c>
-      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15537,9 +14489,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
       <c r="F134" t="n">
         <v>82.23999999999999</v>
       </c>
@@ -15561,7 +14510,6 @@
       <c r="L134" t="n">
         <v>41759.61</v>
       </c>
-      <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -15574,23 +14522,15 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
         <v>174574.28</v>
       </c>
       <c r="F135" t="n">
         <v>116737.37</v>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
         <v>291311.65</v>
       </c>
-      <c r="M135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15603,19 +14543,9 @@
           <t>stUSDS</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
         <v>0</v>
       </c>
-      <c r="M136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -15628,19 +14558,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
         <v>0</v>
       </c>
-      <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15653,25 +14573,18 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
         <v>17144.97</v>
       </c>
       <c r="F138" t="n">
         <v>8259.879999999999</v>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="n">
         <v>3004.45</v>
       </c>
       <c r="L138" t="n">
         <v>28409.3</v>
       </c>
-      <c r="M138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15684,10 +14597,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
         <v>12035.78</v>
       </c>
@@ -15706,7 +14615,6 @@
       <c r="L139" t="n">
         <v>83357.60000000001</v>
       </c>
-      <c r="M139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15719,21 +14627,12 @@
           <t>USDS-GROVE</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="n">
         <v>549.8099999999999</v>
       </c>
       <c r="L140" t="n">
         <v>549.8099999999999</v>
       </c>
-      <c r="M140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15746,12 +14645,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="n">
         <v>2834.56</v>
       </c>
@@ -15764,7 +14657,6 @@
       <c r="L141" t="n">
         <v>8930.969999999999</v>
       </c>
-      <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15777,19 +14669,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
         <v>0</v>
       </c>
-      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15802,23 +14684,15 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
       <c r="F143" t="n">
         <v>10.68</v>
       </c>
       <c r="G143" t="n">
         <v>14.75</v>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
         <v>25.42</v>
       </c>
-      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15831,11 +14705,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>5.66</v>
       </c>
@@ -15851,7 +14720,6 @@
       <c r="L144" t="n">
         <v>1172.97</v>
       </c>
-      <c r="M144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15864,19 +14732,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
         <v>0.01</v>
       </c>
-      <c r="M145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15889,19 +14747,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
         <v>0</v>
       </c>
-      <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15914,19 +14762,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
         <v>0</v>
       </c>
-      <c r="M147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15939,19 +14777,9 @@
           <t>sUSDC</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
         <v>0</v>
       </c>
-      <c r="M148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15964,12 +14792,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
         <v>0.77</v>
       </c>
@@ -15982,7 +14804,6 @@
       <c r="L149" t="n">
         <v>2.37</v>
       </c>
-      <c r="M149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15995,21 +14816,12 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="n">
         <v>0.36</v>
       </c>
       <c r="L150" t="n">
         <v>0.36</v>
       </c>
-      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -16022,19 +14834,9 @@
           <t>stUSDS</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
         <v>0</v>
       </c>
-      <c r="M151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -16047,21 +14849,12 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="n">
         <v>30.6</v>
       </c>
       <c r="L152" t="n">
         <v>30.6</v>
       </c>
-      <c r="M152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -16074,13 +14867,6 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="n">
         <v>21.19</v>
       </c>
@@ -16090,7 +14876,6 @@
       <c r="L153" t="n">
         <v>133.55</v>
       </c>
-      <c r="M153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16103,19 +14888,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
         <v>0</v>
       </c>
-      <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16158,7 +14933,6 @@
       <c r="L155" t="n">
         <v>3.36</v>
       </c>
-      <c r="M155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16171,19 +14945,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
         <v>0</v>
       </c>
-      <c r="M156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16243,14 +15007,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
         <v>76.34</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
         <v>119.5</v>
       </c>
@@ -16280,19 +15039,9 @@
           <t>spUSDC</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
         <v>0</v>
       </c>
-      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16352,19 +15101,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr"/>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
         <v>0.01</v>
       </c>
-      <c r="M161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16501,7 +15240,6 @@
       <c r="L164" t="n">
         <v>3162.43</v>
       </c>
-      <c r="M164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16514,19 +15252,9 @@
           <t>sUSDS</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
         <v>0</v>
       </c>
-      <c r="M165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16723,7 +15451,6 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16774,7 +15501,6 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16825,7 +15551,6 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16953,23 +15678,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>0.01</v>
       </c>
       <c r="G8" t="n">
         <v>0.01</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>0.27</v>
       </c>
       <c r="J8" t="n">
         <v>10.54</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>10.83</v>
       </c>
@@ -16998,22 +15718,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>0.02</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17064,7 +15774,6 @@
       <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17115,7 +15824,6 @@
       <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17166,7 +15874,6 @@
       <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17217,7 +15924,6 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17268,7 +15974,6 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17319,7 +16024,6 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17370,7 +16074,6 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17421,7 +16124,6 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17472,7 +16174,6 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17523,7 +16224,6 @@
       <c r="N19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17614,16 +16314,12 @@
       <c r="I21" t="n">
         <v>0.01</v>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>0.11</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17674,7 +16370,6 @@
       <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17725,7 +16420,6 @@
       <c r="N23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17743,7 +16437,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>4.01</v>
       </c>
@@ -17774,7 +16467,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17792,7 +16484,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>0.03</v>
       </c>
@@ -17823,7 +16514,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17841,11 +16531,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>0.15</v>
       </c>
@@ -17864,7 +16549,6 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17882,8 +16566,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
         <v>216.61</v>
       </c>
@@ -17911,7 +16593,6 @@
       <c r="N27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17929,12 +16610,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
@@ -17950,7 +16625,6 @@
       <c r="N28" t="n">
         <v>0</v>
       </c>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17968,24 +16642,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>14.26</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
         <v>14.26</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18003,22 +16668,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>0.01</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18036,10 +16691,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>4582.17</v>
       </c>
@@ -18061,7 +16712,6 @@
       <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -18079,14 +16729,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
         <v>1262.03</v>
       </c>
@@ -18096,7 +16738,6 @@
       <c r="N32" t="n">
         <v>0</v>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -18114,14 +16755,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>0.55</v>
       </c>
@@ -18131,7 +16764,6 @@
       <c r="N33" t="n">
         <v>0</v>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18149,22 +16781,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>0.01</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18182,22 +16804,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
         <v>0.03</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18248,7 +16860,6 @@
       <c r="N36" t="n">
         <v>0</v>
       </c>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18299,7 +16910,6 @@
       <c r="N37" t="n">
         <v>0</v>
       </c>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18460,7 +17070,6 @@
       <c r="N40" t="n">
         <v>0</v>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18490,11 +17099,6 @@
       <c r="G41" t="n">
         <v>0.59</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
         <v>1378.16</v>
       </c>
@@ -18556,7 +17160,6 @@
       <c r="N42" t="n">
         <v>0</v>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18574,14 +17177,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>65.39</v>
       </c>
@@ -18591,7 +17186,6 @@
       <c r="N43" t="n">
         <v>0</v>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18610,41 +17204,41 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="E44" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="F44" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="G44" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="H44" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="I44" t="n">
-        <v>6953.52</v>
+        <v>17103.06</v>
       </c>
       <c r="J44" t="n">
-        <v>8291.32</v>
+        <v>11730.41</v>
       </c>
       <c r="K44" t="n">
-        <v>12492.55</v>
+        <v>12719.45</v>
       </c>
       <c r="L44" t="n">
-        <v>15124.25</v>
+        <v>14902.21</v>
       </c>
       <c r="M44" t="n">
-        <v>42864.48</v>
+        <v>56462.25</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -18664,38 +17258,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="G45" t="n">
-        <v>6454.4</v>
+        <v>15875.41</v>
       </c>
       <c r="H45" t="n">
-        <v>7020.72</v>
+        <v>17843.96</v>
       </c>
       <c r="I45" t="n">
-        <v>4810.91</v>
+        <v>11833.05</v>
       </c>
       <c r="J45" t="n">
-        <v>4923.13</v>
+        <v>6767.26</v>
       </c>
       <c r="K45" t="n">
-        <v>5594.93</v>
+        <v>5696.55</v>
       </c>
       <c r="L45" t="n">
-        <v>5262.77</v>
+        <v>5185.51</v>
       </c>
       <c r="M45" t="n">
-        <v>39491.94</v>
+        <v>76990.19</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -18716,41 +17308,41 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="E46" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="F46" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="G46" t="n">
-        <v>26.6</v>
+        <v>65.42</v>
       </c>
       <c r="H46" t="n">
-        <v>30.34</v>
+        <v>77.12</v>
       </c>
       <c r="I46" t="n">
-        <v>20.24</v>
+        <v>49.77</v>
       </c>
       <c r="J46" t="n">
-        <v>21.14</v>
+        <v>29.93</v>
       </c>
       <c r="K46" t="n">
-        <v>27.72</v>
+        <v>28.22</v>
       </c>
       <c r="L46" t="n">
-        <v>20.65</v>
+        <v>20.35</v>
       </c>
       <c r="M46" t="n">
-        <v>779.4</v>
+        <v>1803.23</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -18770,9 +17362,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>82.23999999999999</v>
       </c>
@@ -18797,7 +17386,6 @@
       <c r="N47" t="n">
         <v>0</v>
       </c>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -18815,26 +17403,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
         <v>174574.28</v>
       </c>
       <c r="G48" t="n">
         <v>116737.37</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
         <v>291311.65</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -18852,18 +17432,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
         <v>17144.97</v>
       </c>
       <c r="G49" t="n">
         <v>8259.879999999999</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>3004.45</v>
       </c>
@@ -18873,7 +17447,6 @@
       <c r="N49" t="n">
         <v>0</v>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -18891,10 +17464,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>12035.78</v>
       </c>
@@ -18916,7 +17485,6 @@
       <c r="N50" t="n">
         <v>0</v>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -18934,14 +17502,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>549.8099999999999</v>
       </c>
@@ -18951,7 +17511,6 @@
       <c r="N51" t="n">
         <v>0</v>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18969,12 +17528,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>2834.56</v>
       </c>
@@ -18990,7 +17543,6 @@
       <c r="N52" t="n">
         <v>0</v>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19008,26 +17560,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>10.68</v>
       </c>
       <c r="H53" t="n">
         <v>14.75</v>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
         <v>25.42</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -19045,11 +17589,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>5.66</v>
       </c>
@@ -19068,7 +17607,6 @@
       <c r="N54" t="n">
         <v>0</v>
       </c>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19086,22 +17624,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
         <v>0.01</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19119,12 +17647,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>0.77</v>
       </c>
@@ -19140,7 +17662,6 @@
       <c r="N56" t="n">
         <v>0</v>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19158,14 +17679,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>0.36</v>
       </c>
@@ -19175,7 +17688,6 @@
       <c r="N57" t="n">
         <v>0</v>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19193,14 +17705,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
         <v>30.6</v>
       </c>
@@ -19210,7 +17714,6 @@
       <c r="N58" t="n">
         <v>0</v>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19228,13 +17731,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>21.19</v>
       </c>
@@ -19247,7 +17743,6 @@
       <c r="N59" t="n">
         <v>0</v>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19298,7 +17793,6 @@
       <c r="N60" t="n">
         <v>0</v>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19371,14 +17865,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>76.34</v>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
         <v>119.5</v>
       </c>
@@ -19471,22 +17960,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
         <v>0.01</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19537,32 +18016,19 @@
       <c r="N65" t="n">
         <v>0</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>SYNTHETIC &amp; UNPAID (tracked, no beneficiary — notional dr_usd; never pay, never in the payment spreadsheet)</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>all-time total</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19607,7 +18073,6 @@
       <c r="L68" t="n">
         <v>4165.45</v>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>78151.48</v>
       </c>
@@ -19660,7 +18125,6 @@
       <c r="L69" t="n">
         <v>266067.63</v>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>9721633.66</v>
       </c>
@@ -19713,7 +18177,6 @@
       <c r="L70" t="n">
         <v>288.31</v>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
         <v>34254.41</v>
       </c>
@@ -19766,7 +18229,6 @@
       <c r="L71" t="n">
         <v>62.49</v>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>6088.76</v>
       </c>
@@ -19819,7 +18281,6 @@
       <c r="L72" t="n">
         <v>45794.33</v>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
         <v>507291.54</v>
       </c>
@@ -19885,7 +18346,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3318514472871808</v>
+        <v>0.8434382381915353</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -19906,7 +18367,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>177.6857204469182</v>
+        <v>451.6084899754829</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -19927,7 +18388,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3329049989406913</v>
+        <v>0.7642337700311032</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -19948,7 +18409,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.620555888252163e-05</v>
+        <v>0.0001978978972141083</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -19969,7 +18430,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>307.7580186696092</v>
+        <v>706.5050738606662</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -19990,7 +18451,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3339434963263763</v>
+        <v>0.8487554190272794</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -20011,7 +18472,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5425.078324149193</v>
+        <v>13788.45426523544</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -20032,7 +18493,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>147.2736416787795</v>
+        <v>374.3127290389842</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -20053,7 +18514,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3349734848324279</v>
+        <v>0.8239095987975956</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -20074,7 +18535,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6454.40020769498</v>
+        <v>15875.41261142315</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -20095,7 +18556,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26.59639852146469</v>
+        <v>65.41720174133492</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -20116,7 +18577,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.514372319701787</v>
+        <v>3.848949678347971</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -20137,7 +18598,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>7020.719853450289</v>
+        <v>17843.95889316704</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -20158,7 +18619,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30.34189158796749</v>
+        <v>77.11737222651685</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -20179,7 +18640,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6953.518137125108</v>
+        <v>17103.05620594581</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -20200,7 +18661,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4810.914277181574</v>
+        <v>11833.05136508098</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -20221,7 +18682,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20.23617948770795</v>
+        <v>49.77343962389806</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -20242,7 +18703,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8291.323682686629</v>
+        <v>11730.40935177664</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -20263,7 +18724,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4923.134510263595</v>
+        <v>6767.255490013687</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -20284,7 +18745,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21.14386762725331</v>
+        <v>29.93339576463271</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
@@ -20305,7 +18766,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12492.54544984775</v>
+        <v>12719.44814860315</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -20326,7 +18787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5594.92538693962</v>
+        <v>5696.546283555785</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -20347,7 +18808,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.71695008796137</v>
+        <v>28.22037437418672</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -20368,7 +18829,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15124.24692823268</v>
+        <v>14902.20904494357</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -20389,7 +18850,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5262.771706106446</v>
+        <v>5185.50936733331</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -20410,7 +18871,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20.64965082704819</v>
+        <v>20.34649492235729</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -24366,7 +22827,6 @@
       <c r="I4" t="n">
         <v>21644.45</v>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24400,7 +22860,6 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24472,7 +22931,6 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24506,7 +22964,6 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24540,7 +22997,6 @@
       <c r="I9" t="n">
         <v>-692521.38</v>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24612,7 +23068,6 @@
       <c r="I11" t="n">
         <v>480146.96</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24646,7 +23101,6 @@
       <c r="I12" t="n">
         <v>27.21</v>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24794,7 +23248,6 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24828,7 +23281,6 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24862,7 +23314,6 @@
       <c r="I18" t="n">
         <v>0.06</v>
       </c>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24879,16 +23330,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -24896,7 +23347,6 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24930,7 +23380,6 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24964,7 +23413,6 @@
       <c r="I21" t="n">
         <v>3920.16</v>
       </c>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24998,7 +23446,6 @@
       <c r="I22" t="n">
         <v>5018.04</v>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25032,7 +23479,6 @@
       <c r="I23" t="n">
         <v>131.95</v>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25066,7 +23512,6 @@
       <c r="I24" t="n">
         <v>6606.62</v>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25100,7 +23545,6 @@
       <c r="I25" t="n">
         <v>137754.07</v>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25134,7 +23578,6 @@
       <c r="I26" t="n">
         <v>16.03</v>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25168,7 +23611,6 @@
       <c r="I27" t="n">
         <v>13217.46</v>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25202,7 +23644,6 @@
       <c r="I28" t="n">
         <v>0.75</v>
       </c>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25216,22 +23657,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -25254,19 +23695,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -25274,7 +23715,6 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25300,7 +23740,7 @@
         <v>0.01</v>
       </c>
       <c r="G31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -25308,7 +23748,6 @@
       <c r="I31" t="n">
         <v>0.32</v>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25342,7 +23781,6 @@
       <c r="I32" t="n">
         <v>4.98</v>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -25376,7 +23814,6 @@
       <c r="I33" t="n">
         <v>155.3</v>
       </c>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -25396,10 +23833,10 @@
         <v>0.01</v>
       </c>
       <c r="E34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -25410,7 +23847,6 @@
       <c r="I34" t="n">
         <v>0.01</v>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -25444,7 +23880,6 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -25473,12 +23908,11 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -25512,7 +23946,6 @@
       <c r="I37" t="n">
         <v>862.14</v>
       </c>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -25546,7 +23979,6 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -25580,7 +24012,6 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -25614,7 +24045,6 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -25648,7 +24078,6 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -25682,7 +24111,6 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -25716,7 +24144,6 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -25750,7 +24177,6 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25784,7 +24210,6 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25818,7 +24243,6 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25852,7 +24276,6 @@
       <c r="I47" t="n">
         <v>268.39</v>
       </c>
-      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25886,7 +24309,6 @@
       <c r="I48" t="n">
         <v>34.56</v>
       </c>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25976,27 +24398,26 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26030,7 +24451,6 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26047,13 +24467,13 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -26102,7 +24522,6 @@
       <c r="I54" t="n">
         <v>890.66</v>
       </c>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -26136,7 +24555,6 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -26150,29 +24568,29 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="D56" t="n">
-        <v>0.33</v>
+        <v>0.76</v>
       </c>
       <c r="E56" t="n">
-        <v>0.33</v>
+        <v>0.85</v>
       </c>
       <c r="F56" t="n">
-        <v>0.33</v>
+        <v>0.82</v>
       </c>
       <c r="G56" t="n">
-        <v>1.51</v>
+        <v>3.85</v>
       </c>
       <c r="H56" t="n">
-        <v>6953.52</v>
+        <v>17103.06</v>
       </c>
       <c r="I56" t="n">
-        <v>6956.35</v>
+        <v>17110.18</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; flat 0.2% / 12.</t>
+          <t>Skybase synthetic: Pendle SY sUSDS backing; whole wrapper counted once; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -26194,23 +24612,23 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5425.08</v>
+        <v>13788.45</v>
       </c>
       <c r="F57" t="n">
-        <v>6454.4</v>
+        <v>15875.41</v>
       </c>
       <c r="G57" t="n">
-        <v>7020.72</v>
+        <v>17843.96</v>
       </c>
       <c r="H57" t="n">
-        <v>4810.91</v>
+        <v>11833.05</v>
       </c>
       <c r="I57" t="n">
-        <v>23711.11</v>
+        <v>59340.87</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Flagship vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -26226,29 +24644,29 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>177.69</v>
+        <v>451.61</v>
       </c>
       <c r="D58" t="n">
-        <v>307.76</v>
+        <v>706.51</v>
       </c>
       <c r="E58" t="n">
-        <v>147.27</v>
+        <v>374.31</v>
       </c>
       <c r="F58" t="n">
-        <v>26.6</v>
+        <v>65.42</v>
       </c>
       <c r="G58" t="n">
-        <v>30.34</v>
+        <v>77.12</v>
       </c>
       <c r="H58" t="n">
-        <v>20.24</v>
+        <v>49.77</v>
       </c>
       <c r="I58" t="n">
-        <v>709.9</v>
+        <v>1724.74</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds.</t>
+          <t>Skybase synthetic: USDS Risk Capital vault idle + its share of Morpho market idle USDS; no borrowed funds; XR schedule.</t>
         </is>
       </c>
     </row>
@@ -26284,7 +24702,6 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -26313,12 +24730,11 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -26338,7 +24754,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -26352,7 +24768,6 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -26386,7 +24801,6 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -26406,10 +24820,10 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -26420,7 +24834,6 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -26454,7 +24867,6 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26488,7 +24900,6 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -26522,7 +24933,6 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -26556,7 +24966,6 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -26579,10 +24988,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -26590,7 +24999,6 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26624,7 +25032,6 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26658,7 +25065,6 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26692,7 +25098,6 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -26726,7 +25131,6 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26760,7 +25164,6 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26794,7 +25197,6 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26828,7 +25230,6 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26862,7 +25263,6 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -26896,7 +25296,6 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26919,18 +25318,17 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26964,7 +25362,6 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -27074,7 +25471,6 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -27146,7 +25542,6 @@
       <c r="I84" t="n">
         <v>0</v>
       </c>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -27236,7 +25631,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -27248,15 +25643,14 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27290,7 +25684,6 @@
       <c r="I88" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27324,7 +25717,6 @@
       <c r="I89" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
